--- a/data/outplant/sequim/survival.xlsx
+++ b/data/outplant/sequim/survival.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashuffmyer/MyProjects/oysters/polyIC-larvae/data/outplant/sequim/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2A2288-A796-3649-8926-567233A5057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0292DB1-DF25-2F44-B13A-DBAA1DA22DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14240" yWindow="760" windowWidth="14200" windowHeight="16940" xr2:uid="{3D148DFB-94BF-E044-8D7D-CEC1CD506C2E}"/>
+    <workbookView xWindow="31720" yWindow="-780" windowWidth="14200" windowHeight="16940" xr2:uid="{3D148DFB-94BF-E044-8D7D-CEC1CD506C2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="7">
   <si>
     <t>outplant_tag</t>
   </si>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4B1378F-A6DB-0C46-99D1-FAE05B75BC8B}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -460,7 +460,10 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>20251006</v>
+        <v>20250626</v>
+      </c>
+      <c r="D2">
+        <v>131</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -474,7 +477,10 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>20251006</v>
+        <v>20250626</v>
+      </c>
+      <c r="D3">
+        <v>135</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -488,7 +494,10 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>20251006</v>
+        <v>20250626</v>
+      </c>
+      <c r="D4">
+        <v>130</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -502,7 +511,10 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>20251006</v>
+        <v>20250626</v>
+      </c>
+      <c r="D5">
+        <v>134</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -516,7 +528,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>20251006</v>
+        <v>20250626</v>
+      </c>
+      <c r="D6">
+        <v>125</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -530,7 +545,10 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>20251006</v>
+        <v>20250626</v>
+      </c>
+      <c r="D7">
+        <v>116</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -544,7 +562,10 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>20251006</v>
+        <v>20250626</v>
+      </c>
+      <c r="D8">
+        <v>112</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -558,7 +579,10 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>20251006</v>
+        <v>20250626</v>
+      </c>
+      <c r="D9">
+        <v>124</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -572,10 +596,13 @@
         <v>2</v>
       </c>
       <c r="C10">
-        <v>20260531</v>
+        <v>20251006</v>
+      </c>
+      <c r="D10">
+        <v>99</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -586,7 +613,10 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>20260531</v>
+        <v>20251006</v>
+      </c>
+      <c r="D11">
+        <v>104</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -600,7 +630,10 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>20260531</v>
+        <v>20251006</v>
+      </c>
+      <c r="D12">
+        <v>87</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -614,10 +647,13 @@
         <v>3</v>
       </c>
       <c r="C13">
-        <v>20260531</v>
+        <v>20251006</v>
+      </c>
+      <c r="D13">
+        <v>101</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -628,10 +664,13 @@
         <v>2</v>
       </c>
       <c r="C14">
-        <v>20260531</v>
+        <v>20251006</v>
+      </c>
+      <c r="D14">
+        <v>104</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -642,10 +681,13 @@
         <v>3</v>
       </c>
       <c r="C15">
-        <v>20260531</v>
+        <v>20251006</v>
+      </c>
+      <c r="D15">
+        <v>92</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -656,7 +698,10 @@
         <v>3</v>
       </c>
       <c r="C16">
-        <v>20260531</v>
+        <v>20251006</v>
+      </c>
+      <c r="D16">
+        <v>91</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -670,9 +715,148 @@
         <v>2</v>
       </c>
       <c r="C17">
+        <v>20251006</v>
+      </c>
+      <c r="D17">
+        <v>99</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18">
         <v>20260531</v>
       </c>
-      <c r="E17">
+      <c r="D18">
+        <v>98</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>20260531</v>
+      </c>
+      <c r="D19">
+        <v>101</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>20260531</v>
+      </c>
+      <c r="D20">
+        <v>83</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>20260531</v>
+      </c>
+      <c r="D21">
+        <v>96</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>20260531</v>
+      </c>
+      <c r="D22">
+        <v>102</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>20260531</v>
+      </c>
+      <c r="D23">
+        <v>88</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>20260531</v>
+      </c>
+      <c r="D24">
+        <v>87</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>20260531</v>
+      </c>
+      <c r="D25">
+        <v>83</v>
+      </c>
+      <c r="E25">
         <v>0</v>
       </c>
     </row>
